--- a/reports/devops-jobs-israel-2026-W27.xlsx
+++ b/reports/devops-jobs-israel-2026-W27.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-29T11:20:08</t>
+    <t xml:space="preserve">2026-06-30T09:56:14</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -552,6 +552,21 @@
     <t xml:space="preserve">2026-06-26</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-comblack-4434490728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">WINN.AI</t>
   </si>
   <si>
@@ -561,6 +576,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-winn-ai-4432648338</t>
   </si>
   <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer - Modern Workplace</t>
   </si>
   <si>
@@ -576,12 +597,6 @@
     <t xml:space="preserve">2026-06-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kaltura</t>
   </si>
   <si>
@@ -591,885 +606,813 @@
     <t xml:space="preserve">2026-06-21</t>
   </si>
   <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4431049288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal Recruiting &amp; Placement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-michal-recruiting-placement-4434952736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NSO Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nso-group-4431918133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-varonis-4434746747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">Discreet Company</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4431047248</t>
   </si>
   <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4431049288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+    <t xml:space="preserve">ODDITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4431091730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4432560554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4432565182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (35679)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-35679-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434278425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4430658020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס/ת DEVOPS ותמיכת תשתיות מחשוב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-devops-%D7%95%D7%AA%D7%9E%D7%99%D7%9B%D7%AA-%D7%AA%D7%A9%D7%AA%D7%99%D7%95%D7%AA-%D7%9E%D7%97%D7%A9%D7%95%D7%91-at-elad-software-systems-4434494489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech Lead – Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tech-lead-%E2%80%93-cloud-devops-engineer-at-maytronics-4434952849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops TL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tl-at-nova-ltd-4430216198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-proteantecs-4432578072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4431046130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Backend Engineer (GCP Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azimut.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-backend-engineer-gcp-infrastructure-at-azimut-ai-4422252173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-23</t>
   </si>
   <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4432560554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
+    <t xml:space="preserve">DevOps engineer (Data Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-platform-at-moveo-source-4433615314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-shavit-software-4432535487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-sqlink-group-4431082699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SearchApi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-searchapi-4434496090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (35684)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434276396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4434448757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4434284102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturing Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manufacturing-infrastructure-engineer-at-quantum-machines-4434304423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4429824285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4434703088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspect Imaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-aspect-imaging-4434489230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM &amp; System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpticSolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/pm-system-engineer-at-opticsolution-4431848577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4433035881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-confidential-careers-4431040388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-confidential-4434124801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPS-JOBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-sps-jobs-4431035610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking, Virtualization, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-compie-technologies-4434281959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
   </si>
   <si>
     <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4432547601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4434430161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onyx Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-onyx-security-4433485039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comblack-4433308890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4434293341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4431046130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4428946633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer [Contracting]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theory Ventures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-contracting-at-theory-ventures-4432553221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior platform engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-team-leader-at-evoke-4431694215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founding Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stepscale.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-platform-engineer-at-stepscale-io-4432091419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4431060955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4430658020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetNut.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-kpmg-israel-4430569211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer (Data Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-platform-at-moveo-source-4433615314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer &amp; Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-tech-lead-at-mobileye-4366001366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-workday-4420737999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noma Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-noma-security-4431203415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (35679)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-35679-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434278425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ycon-devops-alm-services-ltd-4431061443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-shavit-software-4432535487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vectorious Medical Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4434446138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMOS-Spacecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-amos-spacecom-4430211390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434276396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4432202668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4434284102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4434448757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4429824285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM &amp; System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpticSolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/pm-system-engineer-at-opticsolution-4431848577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-confidential-careers-4431040388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-compie-technologies-4434281959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4432603109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4429863387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
   </si>
   <si>
@@ -1500,15 +1443,24 @@
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD, Git</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1524,16 +1476,16 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1685,7 +1637,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -1693,7 +1645,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1701,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1709,7 +1661,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>786</v>
+        <v>803</v>
       </c>
     </row>
     <row r="10">
@@ -1781,7 +1733,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -1808,36 +1760,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>493</v>
+        <v>432</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1856,47 +1808,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>497</v>
+        <v>396</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>409</v>
+        <v>481</v>
       </c>
       <c r="B3" s="3">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
@@ -1904,79 +1856,79 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>503</v>
+        <v>395</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>408</v>
+        <v>487</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>411</v>
+        <v>488</v>
       </c>
       <c r="B15" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>504</v>
+        <v>314</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -2004,13 +1956,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
@@ -2021,10 +1973,10 @@
         <v>36</v>
       </c>
       <c r="C2" s="3">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2033,88 +1985,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3">
-        <v>36.7</v>
+        <v>30.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.9</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.5</v>
+        <v>32.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.1</v>
+        <v>21.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2127,7 +2079,7 @@
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2198,7 +2150,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -2230,7 +2182,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -2262,7 +2214,7 @@
         <v>48</v>
       </c>
       <c r="J4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -2294,7 +2246,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -2326,7 +2278,7 @@
         <v>48</v>
       </c>
       <c r="J6" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -2358,7 +2310,7 @@
         <v>48</v>
       </c>
       <c r="J7" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -2390,7 +2342,7 @@
         <v>62</v>
       </c>
       <c r="J8" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -2422,7 +2374,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -2454,7 +2406,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -2486,7 +2438,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -2518,7 +2470,7 @@
         <v>76</v>
       </c>
       <c r="J12" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -2550,7 +2502,7 @@
         <v>80</v>
       </c>
       <c r="J13" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -2582,7 +2534,7 @@
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -2614,7 +2566,7 @@
         <v>89</v>
       </c>
       <c r="J15" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2646,7 +2598,7 @@
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -2678,7 +2630,7 @@
         <v>97</v>
       </c>
       <c r="J17" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -2710,7 +2662,7 @@
         <v>102</v>
       </c>
       <c r="J18" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -2742,7 +2694,7 @@
         <v>105</v>
       </c>
       <c r="J19" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -2774,7 +2726,7 @@
         <v>109</v>
       </c>
       <c r="J20" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
@@ -2806,7 +2758,7 @@
         <v>102</v>
       </c>
       <c r="J21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -2838,7 +2790,7 @@
         <v>44</v>
       </c>
       <c r="J22" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -2870,7 +2822,7 @@
         <v>121</v>
       </c>
       <c r="J23" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -2902,7 +2854,7 @@
         <v>125</v>
       </c>
       <c r="J24" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -2934,7 +2886,7 @@
         <v>130</v>
       </c>
       <c r="J25" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -2966,7 +2918,7 @@
         <v>109</v>
       </c>
       <c r="J26" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
@@ -2998,7 +2950,7 @@
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
@@ -3030,7 +2982,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
@@ -3062,7 +3014,7 @@
         <v>102</v>
       </c>
       <c r="J29" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -3094,7 +3046,7 @@
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
@@ -3126,7 +3078,7 @@
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32">
@@ -3158,7 +3110,7 @@
         <v>159</v>
       </c>
       <c r="J32" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
@@ -3190,7 +3142,7 @@
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -3220,7 +3172,7 @@
         <v>167</v>
       </c>
       <c r="J34" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
@@ -3252,7 +3204,7 @@
         <v>109</v>
       </c>
       <c r="J35" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -3282,21 +3234,21 @@
         <v>176</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>59</v>
@@ -3306,27 +3258,27 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>59</v>
@@ -3336,13 +3288,13 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -3372,21 +3324,21 @@
         <v>44</v>
       </c>
       <c r="J39" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>59</v>
@@ -3396,13 +3348,13 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J40" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3410,10 +3362,10 @@
         <v>138</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>58</v>
@@ -3426,54 +3378,54 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>63</v>
+        <v>195</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>184</v>
+        <v>44</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>147</v>
@@ -3486,43 +3438,43 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>199</v>
+        <v>63</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="J44" s="3">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -3530,10 +3482,10 @@
         <v>138</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>147</v>
@@ -3546,13 +3498,13 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="J45" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3560,10 +3512,10 @@
         <v>138</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>58</v>
@@ -3576,51 +3528,51 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="J46" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="J47" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>174</v>
@@ -3636,24 +3588,24 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>58</v>
@@ -3661,28 +3613,26 @@
       <c r="E49" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>174</v>
@@ -3693,20 +3643,18 @@
       <c r="E50" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J50" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3714,13 +3662,13 @@
         <v>138</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>59</v>
@@ -3730,40 +3678,42 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="J51" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>138</v>
+        <v>56</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F52" s="3"/>
+      <c r="F52" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="J52" s="3">
         <v>5</v>
@@ -3771,13 +3721,13 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>58</v>
@@ -3785,7 +3735,9 @@
       <c r="E53" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
@@ -3793,21 +3745,21 @@
         <v>229</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>191</v>
+        <v>70</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>58</v>
@@ -3823,40 +3775,40 @@
         <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>233</v>
+        <v>76</v>
       </c>
       <c r="J54" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>234</v>
+        <v>138</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>236</v>
+        <v>179</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>147</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
@@ -3864,10 +3816,10 @@
         <v>138</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>147</v>
@@ -3880,10 +3832,10 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J56" s="3">
         <v>0</v>
@@ -3891,16 +3843,16 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>240</v>
+        <v>172</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>242</v>
+        <v>183</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>243</v>
+        <v>58</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>59</v>
@@ -3910,21 +3862,21 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>63</v>
+        <v>239</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>174</v>
@@ -3940,27 +3892,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>59</v>
@@ -3970,27 +3922,27 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>59</v>
@@ -4000,24 +3952,24 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>252</v>
+        <v>63</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>58</v>
@@ -4030,27 +3982,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>59</v>
@@ -4060,43 +4012,43 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="J62" s="3">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>258</v>
+        <v>138</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="J63" s="3">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
@@ -4104,10 +4056,10 @@
         <v>94</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>262</v>
+        <v>174</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>58</v>
@@ -4120,27 +4072,27 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>44</v>
+        <v>256</v>
       </c>
       <c r="J64" s="3">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>174</v>
+        <v>259</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>58</v>
+        <v>260</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>59</v>
@@ -4150,57 +4102,57 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="J65" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>147</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="J66" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>59</v>
@@ -4210,30 +4162,30 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>138</v>
+        <v>269</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>270</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
@@ -4243,10 +4195,10 @@
         <v>271</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="J68" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -4263,7 +4215,7 @@
         <v>58</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
@@ -4273,48 +4225,48 @@
         <v>274</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J69" s="3">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>277</v>
-      </c>
       <c r="D70" s="3" t="s">
-        <v>278</v>
+        <v>58</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="J70" s="3">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>174</v>
@@ -4330,87 +4282,87 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>283</v>
+        <v>44</v>
       </c>
       <c r="J71" s="3">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>284</v>
+        <v>138</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>70</v>
+        <v>209</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>286</v>
+        <v>59</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="J72" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>203</v>
+        <v>284</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>59</v>
+        <v>285</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="J73" s="3">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>70</v>
+        <v>289</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>59</v>
@@ -4420,24 +4372,24 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="J74" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>147</v>
@@ -4450,27 +4402,27 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>48</v>
       </c>
       <c r="J75" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>59</v>
@@ -4480,24 +4432,24 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>167</v>
       </c>
       <c r="J76" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>147</v>
@@ -4510,27 +4462,27 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>59</v>
@@ -4540,113 +4492,111 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="J78" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>308</v>
+        <v>63</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>201</v>
+        <v>305</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>147</v>
+        <v>306</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>310</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>63</v>
+        <v>308</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>214</v>
+        <v>309</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>313</v>
+        <v>138</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>182</v>
+        <v>289</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>147</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="J81" s="3">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>174</v>
@@ -4658,27 +4608,27 @@
         <v>59</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>218</v>
+        <v>314</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>205</v>
+        <v>253</v>
       </c>
       <c r="J82" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>319</v>
+        <v>138</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>174</v>
@@ -4694,24 +4644,24 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>184</v>
+        <v>318</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>58</v>
@@ -4724,51 +4674,53 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>327</v>
+        <v>174</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F85" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
       <c r="J85" s="3">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>174</v>
@@ -4784,114 +4736,116 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>159</v>
       </c>
       <c r="J86" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="J87" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>336</v>
+        <v>174</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>216</v>
+        <v>333</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>138</v>
+        <v>334</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>339</v>
+        <v>209</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>138</v>
+        <v>334</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>58</v>
@@ -4899,26 +4853,28 @@
       <c r="E90" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F90" s="3"/>
+      <c r="F90" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="J90" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>174</v>
@@ -4929,34 +4885,32 @@
       <c r="E91" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I91" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J91" s="3">
         <v>44</v>
-      </c>
-      <c r="J91" s="3">
-        <v>45</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>38</v>
@@ -4966,27 +4920,27 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J92" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>59</v>
@@ -4996,24 +4950,24 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="J93" s="3">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>138</v>
+        <v>348</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>353</v>
+        <v>247</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>147</v>
@@ -5026,59 +4980,57 @@
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>355</v>
+        <v>221</v>
       </c>
       <c r="J94" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>191</v>
+        <v>351</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>138</v>
+        <v>345</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>191</v>
+        <v>354</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>58</v>
+        <v>355</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>59</v>
@@ -5088,24 +5040,24 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>58</v>
@@ -5113,64 +5065,64 @@
       <c r="E97" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F97" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="J97" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="J98" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>367</v>
+        <v>174</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>59</v>
@@ -5180,24 +5132,24 @@
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="J99" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>147</v>
@@ -5210,10 +5162,10 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="J100" s="3">
         <v>1</v>
@@ -5221,13 +5173,13 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>371</v>
+        <v>178</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>367</v>
+        <v>179</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>147</v>
@@ -5240,54 +5192,54 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="J101" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>277</v>
+        <v>371</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>278</v>
+        <v>147</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="J102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>376</v>
+        <v>263</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>336</v>
+        <v>264</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>147</v>
@@ -5295,31 +5247,29 @@
       <c r="E103" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F103" s="3" t="s">
-        <v>310</v>
-      </c>
+      <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="J103" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>147</v>
@@ -5332,54 +5282,56 @@
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="J104" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>381</v>
+        <v>258</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F105" s="3"/>
+      <c r="F105" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="G105" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="J105" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>383</v>
+        <v>345</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>339</v>
+        <v>382</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>147</v>
@@ -5392,24 +5344,24 @@
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="J106" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>58</v>
@@ -5418,46 +5370,46 @@
         <v>59</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J107" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>301</v>
+        <v>369</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>147</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J108" s="3">
         <v>0</v>
@@ -5465,126 +5417,36 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>301</v>
+        <v>369</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>147</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J109" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J110" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J111" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="J112" s="3">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J112"/>
+  <autoFilter ref="A1:J109"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5694,9 +5556,6 @@
     <hyperlink ref="H107" r:id="rId106"/>
     <hyperlink ref="H108" r:id="rId107"/>
     <hyperlink ref="H109" r:id="rId108"/>
-    <hyperlink ref="H110" r:id="rId109"/>
-    <hyperlink ref="H111" r:id="rId110"/>
-    <hyperlink ref="H112" r:id="rId111"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5704,8 +5563,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5738,13 +5597,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5752,7 +5611,7 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3">
@@ -5760,10 +5619,10 @@
         <v>138</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5771,18 +5630,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5790,18 +5649,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>197</v>
+        <v>70</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5809,7 +5668,7 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6">
@@ -5817,10 +5676,10 @@
         <v>138</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5828,18 +5687,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5847,18 +5706,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5866,18 +5725,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>191</v>
+        <v>264</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5885,18 +5744,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5904,18 +5763,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5923,18 +5782,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5942,18 +5801,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>323</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5961,18 +5820,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>138</v>
+        <v>367</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>338</v>
+        <v>178</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>339</v>
+        <v>179</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5980,18 +5839,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>316</v>
+        <v>369</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5999,18 +5858,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>138</v>
+        <v>345</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>191</v>
+        <v>382</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6018,18 +5877,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>379</v>
+        <v>179</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6037,18 +5896,18 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -6056,68 +5915,11 @@
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G18"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6136,9 +5938,6 @@
     <hyperlink ref="G16" r:id="rId15"/>
     <hyperlink ref="G17" r:id="rId16"/>
     <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6152,15 +5951,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B2" s="3">
         <v>29</v>
@@ -6168,7 +5967,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -6176,7 +5975,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -6184,7 +5983,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
@@ -6192,7 +5991,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="B6" s="3">
         <v>16</v>
@@ -6200,15 +5999,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>310</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>170</v>
+        <v>361</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -6216,15 +6015,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>409</v>
+        <v>314</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -6232,7 +6031,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -6240,7 +6039,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -6248,7 +6047,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -6256,7 +6055,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6264,7 +6063,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6272,7 +6071,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6285,7 +6084,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6294,7 +6093,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
@@ -6339,23 +6138,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>127</v>
+        <v>316</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6363,7 +6162,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6371,7 +6170,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>196</v>
+        <v>142</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6379,7 +6178,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6387,7 +6186,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6395,7 +6194,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6403,7 +6202,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6411,7 +6210,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6432,16 +6231,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
@@ -6575,13 +6374,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>139</v>
+        <v>316</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>4.0</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6589,13 +6388,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6603,13 +6402,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>214</v>
+        <v>139</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6617,13 +6416,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6631,10 +6430,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>200</v>
+        <v>263</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6645,13 +6444,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6671,15 +6470,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6693,10 +6492,10 @@
         <v>59</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4">
@@ -6704,10 +6503,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -6726,7 +6525,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2">
@@ -6734,7 +6533,7 @@
         <v>58</v>
       </c>
       <c r="B2" s="3">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -6742,7 +6541,7 @@
         <v>147</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -6755,23 +6554,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>165</v>
+        <v>260</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>278</v>
+        <v>135</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -6779,7 +6578,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6787,7 +6586,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>299</v>
+        <v>355</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6802,7 +6601,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6814,10 +6613,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6829,10 +6628,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6849,28 +6648,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>89</v>
@@ -6881,31 +6680,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="F3" s="3">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -6913,31 +6712,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>434</v>
+        <v>287</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>435</v>
+        <v>288</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>174</v>
+        <v>289</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="F4" s="3">
         <v>76</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>438</v>
+        <v>290</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>80</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5">
@@ -6945,31 +6744,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="F5" s="3">
         <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6">
@@ -6977,31 +6776,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>301</v>
+        <v>421</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>209</v>
+        <v>422</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>216</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
@@ -7009,31 +6808,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>174</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="F7" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -7041,31 +6840,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>174</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F8" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9">
@@ -7073,7 +6872,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>155</v>
@@ -7082,19 +6881,19 @@
         <v>156</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="F9" s="3">
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>44</v>
@@ -7114,13 +6913,13 @@
         <v>70</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="F10" s="3">
         <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>24</v>
@@ -7137,28 +6936,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="F11" s="3">
         <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -7169,31 +6968,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>456</v>
+        <v>345</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>457</v>
+        <v>316</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>242</v>
+        <v>346</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="F12" s="3">
         <v>40</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>459</v>
+        <v>347</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>460</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -7201,31 +7000,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>366</v>
+        <v>287</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>341</v>
+        <v>443</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>367</v>
+        <v>179</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="F13" s="3">
         <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>368</v>
+        <v>445</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>80</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
@@ -7233,31 +7032,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>174</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="F14" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>220</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -7265,31 +7064,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="F15" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
@@ -7297,31 +7096,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>295</v>
+        <v>456</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="F16" s="3">
         <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17">
@@ -7329,31 +7128,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="F17" s="3">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18">
@@ -7361,31 +7160,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>482</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
@@ -7393,31 +7192,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="F19" s="3">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -7425,31 +7224,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -7457,31 +7256,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>493</v>
+        <v>417</v>
       </c>
       <c r="F21" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W27.xlsx
+++ b/reports/devops-jobs-israel-2026-W27.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-30T09:56:14</t>
+    <t xml:space="preserve">2026-07-01T10:06:26</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9%</t>
+    <t xml:space="preserve">1.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -252,334 +252,544 @@
     <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer, Application Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, ELK/Elastic, Service Mesh, Kafka, RabbitMQ, Networking, Security, Argo CD, Observability, Crossplane, Flux/GitOps, Container Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7955819/?gh_jid=7955819</t>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Services DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Services DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Ansible, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4432560554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4431046130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4431091730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zafran Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4433814215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-comblack-4434490728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal Recruiting &amp; Placement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-michal-recruiting-placement-4434952736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4435550223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-proteantecs-4432578072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4431047248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4435389030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Admin &amp; DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-admin-devops-at-ycon-devops-alm-services-ltd-4431921150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WINN.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-winn-ai-4432648338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorious Medical Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4434446138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyeviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4431959175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Services DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Services DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Ansible, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587301002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4433814215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-comblack-4434490728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINN.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-winn-ai-4432648338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4435542128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer - Modern Workplace</t>
@@ -588,255 +798,207 @@
     <t xml:space="preserve">Jobgether</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-modern-workplace-at-jobgether-4433676136</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4431365664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4431049288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michal Recruiting &amp; Placement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-michal-recruiting-placement-4434952736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NSO Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nso-group-4431918133</t>
+    <t xml:space="preserve">Skill Mind Tech Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-skill-mind-tech-bridge-4435107299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODDITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer | Leading Company (5466)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-leading-company-5466-at-ingima-4434986901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס/ת DEVOPS ותמיכת תשתיות מחשוב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-devops-%D7%95%D7%AA%D7%9E%D7%99%D7%9B%D7%AA-%D7%AA%D7%A9%D7%AA%D7%99%D7%95%D7%AA-%D7%9E%D7%97%D7%A9%D7%95%D7%91-at-elad-software-systems-4434494489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Varonis</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-varonis-4434746747</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Moon Active</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech Lead – Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tech-lead-%E2%80%93-cloud-devops-engineer-at-maytronics-4434952849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Play Perfect</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4431047248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4432541955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4431091730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4432560554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4432565182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4434703088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer (35679)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-35679-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434278425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4430658020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4432517539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס/ת DEVOPS ותמיכת תשתיות מחשוב</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-devops-%D7%95%D7%AA%D7%9E%D7%99%D7%9B%D7%AA-%D7%AA%D7%A9%D7%AA%D7%99%D7%95%D7%AA-%D7%9E%D7%97%D7%A9%D7%95%D7%91-at-elad-software-systems-4434494489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech Lead – Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tech-lead-%E2%80%93-cloud-devops-engineer-at-maytronics-4434952849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops TL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tl-at-nova-ltd-4430216198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-proteantecs-4432578072</t>
-  </si>
-  <si>
     <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
   </si>
   <si>
@@ -846,619 +1008,319 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
   </si>
   <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4431046130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4429840763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Backend Engineer (GCP Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azimut.ai</t>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Reliability Engineer MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-audiocodes-4435108288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4432603109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior platform engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-backend-engineer-gcp-infrastructure-at-azimut-ai-4422252173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4432211748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer (Data Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-platform-at-moveo-source-4433615314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW DevOps and Test Infrastructure Student, Nitro SW Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Terraform/IaC, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-devops-and-test-infrastructure-student-nitro-sw-team-at-amazon-web-services-aws-4432816876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC &amp; SOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-soc-analyst-at-commit-4421804878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4428923734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4422723294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
     <t xml:space="preserve">Shavit Software</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-shavit-software-4432535487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-sqlink-group-4431082699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SearchApi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-searchapi-4434496090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434276396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4434448757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4434284102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufacturing Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manufacturing-infrastructure-engineer-at-quantum-machines-4434304423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4429824285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4434703088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aspect Imaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-aspect-imaging-4434489230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM &amp; System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpticSolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/pm-system-engineer-at-opticsolution-4431848577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4433035881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-confidential-careers-4431040388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-confidential-4434124801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPS-JOBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-sps-jobs-4431035610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking, Virtualization, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-compie-technologies-4434281959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-shavit-software-4426784526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1467,25 +1329,25 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
+    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1637,7 +1499,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -1645,7 +1507,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1653,7 +1515,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -1661,7 +1523,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>803</v>
+        <v>813</v>
       </c>
     </row>
     <row r="10">
@@ -1733,7 +1595,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -1741,7 +1603,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1760,28 +1622,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>406</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>432</v>
+        <v>383</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1789,7 +1651,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1808,130 +1670,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>480</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>481</v>
+        <v>355</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>482</v>
+        <v>436</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>484</v>
+        <v>331</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>361</v>
+        <v>439</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>486</v>
+        <v>440</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>399</v>
+        <v>358</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>395</v>
+        <v>441</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>487</v>
+        <v>353</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>393</v>
+        <v>442</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>488</v>
+        <v>352</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1956,13 +1818,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>489</v>
+        <v>443</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>490</v>
+        <v>444</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>491</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2">
@@ -1970,13 +1832,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3">
-        <v>12.1</v>
+        <v>13.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>492</v>
+        <v>446</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1985,19 +1847,19 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3">
-        <v>30.6</v>
+        <v>57.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>492</v>
+        <v>446</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>493</v>
+        <v>447</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -2006,67 +1868,67 @@
         <v>8.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>492</v>
+        <v>446</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>494</v>
+        <v>448</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.5</v>
+        <v>3.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>492</v>
+        <v>446</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>495</v>
+        <v>449</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.3</v>
+        <v>28.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>492</v>
+        <v>446</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>496</v>
+        <v>450</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>21.5</v>
+        <v>19.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>492</v>
+        <v>446</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>497</v>
+        <v>451</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>492</v>
+        <v>446</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2077,8 +1939,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2150,7 +2012,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -2182,7 +2044,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -2214,7 +2076,7 @@
         <v>48</v>
       </c>
       <c r="J4" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -2246,7 +2108,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -2278,7 +2140,7 @@
         <v>48</v>
       </c>
       <c r="J6" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -2310,7 +2172,7 @@
         <v>48</v>
       </c>
       <c r="J7" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -2342,7 +2204,7 @@
         <v>62</v>
       </c>
       <c r="J8" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -2374,7 +2236,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -2406,7 +2268,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -2438,7 +2300,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -2470,7 +2332,7 @@
         <v>76</v>
       </c>
       <c r="J12" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -2478,63 +2340,63 @@
         <v>77</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J14" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -2542,31 +2404,31 @@
         <v>86</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -2574,10 +2436,10 @@
         <v>90</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>58</v>
@@ -2586,19 +2448,19 @@
         <v>59</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J16" s="3">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2606,39 +2468,39 @@
         <v>94</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J17" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>58</v>
@@ -2650,27 +2512,27 @@
         <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="J18" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>58</v>
@@ -2694,7 +2556,7 @@
         <v>105</v>
       </c>
       <c r="J19" s="3">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -2702,7 +2564,7 @@
         <v>106</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>58</v>
@@ -2723,18 +2585,18 @@
         <v>108</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="J20" s="3">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>58</v>
@@ -2746,30 +2608,30 @@
         <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="J21" s="3">
-        <v>16</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>58</v>
@@ -2778,30 +2640,30 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="J22" s="3">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>58</v>
@@ -2822,7 +2684,7 @@
         <v>121</v>
       </c>
       <c r="J23" s="3">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
@@ -2830,48 +2692,48 @@
         <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J24" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>128</v>
@@ -2883,24 +2745,24 @@
         <v>129</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="J25" s="3">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
@@ -2915,56 +2777,56 @@
         <v>133</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>134</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>59</v>
@@ -2979,56 +2841,56 @@
         <v>141</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="J28" s="3">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>38</v>
@@ -3046,7 +2908,7 @@
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
@@ -3057,7 +2919,7 @@
         <v>151</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>58</v>
@@ -3066,30 +2928,30 @@
         <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="J31" s="3">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>58</v>
@@ -3107,31 +2969,29 @@
         <v>158</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>159</v>
+        <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>161</v>
-      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
@@ -3139,40 +2999,42 @@
         <v>162</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="J33" s="3">
-        <v>49</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="J34" s="3">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
@@ -3183,33 +3045,31 @@
         <v>169</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>170</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="J35" s="3">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>173</v>
@@ -3218,7 +3078,7 @@
         <v>174</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>59</v>
@@ -3231,24 +3091,24 @@
         <v>175</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="J36" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>59</v>
@@ -3258,24 +3118,24 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>58</v>
@@ -3288,27 +3148,27 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J38" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>59</v>
@@ -3318,13 +3178,13 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J39" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3338,7 +3198,7 @@
         <v>189</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>59</v>
@@ -3351,21 +3211,21 @@
         <v>190</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>191</v>
+        <v>48</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>58</v>
@@ -3384,7 +3244,7 @@
         <v>194</v>
       </c>
       <c r="J41" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -3395,10 +3255,10 @@
         <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>59</v>
@@ -3408,13 +3268,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J42" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -3428,7 +3288,7 @@
         <v>201</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>59</v>
@@ -3441,7 +3301,7 @@
         <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J43" s="3">
         <v>1</v>
@@ -3449,29 +3309,29 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J44" s="3">
         <v>1</v>
@@ -3479,19 +3339,19 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
@@ -3501,15 +3361,15 @@
         <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>208</v>
@@ -3518,7 +3378,7 @@
         <v>209</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>59</v>
@@ -3528,10 +3388,10 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="J46" s="3">
         <v>0</v>
@@ -3539,13 +3399,13 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>138</v>
+        <v>213</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>58</v>
@@ -3553,15 +3413,17 @@
       <c r="E47" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="J47" s="3">
         <v>0</v>
@@ -3569,43 +3431,43 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>138</v>
+        <v>217</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="J48" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>58</v>
@@ -3618,27 +3480,27 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="J49" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>58</v>
+        <v>225</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>59</v>
@@ -3648,121 +3510,117 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>58</v>
+        <v>225</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>56</v>
+        <v>229</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>225</v>
-      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="J52" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>228</v>
+        <v>63</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>225</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="J53" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>68</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>59</v>
@@ -3772,27 +3630,27 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J54" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>59</v>
@@ -3802,27 +3660,27 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="J55" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>59</v>
@@ -3832,54 +3690,54 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="J57" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>58</v>
@@ -3892,27 +3750,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>242</v>
+        <v>122</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>59</v>
@@ -3922,27 +3780,27 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="J59" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>246</v>
+        <v>122</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>59</v>
@@ -3952,57 +3810,57 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>63</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>255</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>138</v>
+        <v>257</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>200</v>
+        <v>258</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>59</v>
@@ -4012,27 +3870,27 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="J62" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>59</v>
@@ -4042,24 +3900,24 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="J63" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>58</v>
@@ -4072,27 +3930,27 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="J64" s="3">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>59</v>
@@ -4102,117 +3960,119 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>264</v>
+        <v>192</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>266</v>
+        <v>56</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>227</v>
+        <v>276</v>
       </c>
       <c r="J68" s="3">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>59</v>
@@ -4222,27 +4082,27 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="J69" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>94</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>276</v>
+        <v>209</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>59</v>
@@ -4252,54 +4112,54 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>44</v>
+        <v>186</v>
       </c>
       <c r="J70" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>174</v>
+        <v>251</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>44</v>
+        <v>285</v>
       </c>
       <c r="J71" s="3">
-        <v>46</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>138</v>
+        <v>286</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>209</v>
+        <v>70</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>58</v>
@@ -4312,57 +4172,57 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>191</v>
+        <v>76</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>285</v>
+        <v>59</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>167</v>
+        <v>292</v>
       </c>
       <c r="J73" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>287</v>
+        <v>122</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>289</v>
+        <v>192</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>59</v>
@@ -4372,27 +4232,27 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>291</v>
+        <v>90</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>293</v>
+        <v>192</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>59</v>
@@ -4402,84 +4262,84 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>48</v>
+        <v>297</v>
       </c>
       <c r="J75" s="3">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="J76" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>299</v>
+        <v>192</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>301</v>
+        <v>122</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>58</v>
@@ -4492,57 +4352,59 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>63</v>
+        <v>308</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>305</v>
+        <v>180</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>306</v>
+        <v>58</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F79" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>209</v>
+        <v>312</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>59</v>
@@ -4552,27 +4414,27 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="J80" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>138</v>
+        <v>310</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>288</v>
+        <v>173</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>289</v>
+        <v>174</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>59</v>
@@ -4582,24 +4444,24 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="J81" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>58</v>
@@ -4607,34 +4469,32 @@
       <c r="E82" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>314</v>
-      </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="J82" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>138</v>
+        <v>318</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>316</v>
+        <v>200</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>59</v>
@@ -4644,27 +4504,27 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>318</v>
+        <v>186</v>
       </c>
       <c r="J83" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>59</v>
@@ -4677,10 +4537,10 @@
         <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>191</v>
+        <v>48</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85">
@@ -4691,17 +4551,15 @@
         <v>323</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>225</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
@@ -4709,744 +4567,196 @@
         <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>44</v>
+        <v>325</v>
       </c>
       <c r="J85" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
       <c r="J86" s="3">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>138</v>
+        <v>329</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>331</v>
+      </c>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>174</v>
+        <v>335</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>333</v>
+        <v>212</v>
       </c>
       <c r="J88" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>209</v>
+        <v>70</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>225</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>209</v>
+        <v>342</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>58</v>
+        <v>343</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>225</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>341</v>
+        <v>163</v>
       </c>
       <c r="J91" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J93" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J94" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J95" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J96" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="J97" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J98" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J100" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J103" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="J104" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="J105" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J106" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J107" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J108" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J109" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J109"/>
+  <autoFilter ref="A1:J91"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5538,24 +4848,6 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
-    <hyperlink ref="H92" r:id="rId91"/>
-    <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
-    <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
-    <hyperlink ref="H103" r:id="rId102"/>
-    <hyperlink ref="H104" r:id="rId103"/>
-    <hyperlink ref="H105" r:id="rId104"/>
-    <hyperlink ref="H106" r:id="rId105"/>
-    <hyperlink ref="H107" r:id="rId106"/>
-    <hyperlink ref="H108" r:id="rId107"/>
-    <hyperlink ref="H109" r:id="rId108"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5563,8 +4855,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5597,13 +4889,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5611,18 +4903,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>138</v>
+        <v>213</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5630,18 +4922,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>138</v>
+        <v>222</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5649,18 +4941,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>138</v>
+        <v>229</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>70</v>
+        <v>231</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5668,18 +4960,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5687,18 +4979,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>239</v>
+        <v>63</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5706,18 +4998,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5725,18 +5017,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>264</v>
+        <v>204</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5744,18 +5036,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>289</v>
+        <v>201</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5763,18 +5055,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>209</v>
+        <v>335</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5782,144 +5074,11 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>389</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5931,13 +5090,6 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5951,47 +5103,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>392</v>
+        <v>350</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>393</v>
+        <v>351</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>394</v>
+        <v>352</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>395</v>
+        <v>353</v>
       </c>
       <c r="B6" s="3">
         <v>16</v>
@@ -5999,71 +5151,71 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>361</v>
+        <v>331</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>314</v>
+        <v>354</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>396</v>
+        <v>355</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>397</v>
+        <v>356</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>398</v>
+        <v>357</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>399</v>
+        <v>358</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>400</v>
+        <v>359</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>401</v>
+        <v>360</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6071,10 +5223,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>402</v>
+        <v>361</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6084,7 +5236,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6093,7 +5245,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
@@ -6106,7 +5258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -6114,7 +5266,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6130,7 +5282,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>69</v>
+        <v>188</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6138,23 +5290,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>69</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>316</v>
+        <v>113</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6162,7 +5314,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6170,7 +5322,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6178,7 +5330,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6186,7 +5338,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6194,7 +5346,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>200</v>
+        <v>281</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6202,7 +5354,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>211</v>
+        <v>290</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6210,7 +5362,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>219</v>
+        <v>299</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6224,23 +5376,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>403</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
@@ -6248,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C2" s="3">
         <v>19.2</v>
@@ -6276,7 +5428,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C4" s="3">
         <v>15.1</v>
@@ -6290,10 +5442,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3">
-        <v>14.3</v>
+        <v>10.9</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -6304,13 +5456,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="C6" s="3">
-        <v>10.9</v>
+        <v>7.3</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6318,10 +5470,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="C7" s="3">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -6332,10 +5484,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="C8" s="3">
-        <v>6.2</v>
+        <v>5.0</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6346,10 +5498,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3">
-        <v>5.0</v>
+        <v>4.6</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6360,7 +5512,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C10" s="3">
         <v>4.3</v>
@@ -6374,10 +5526,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>316</v>
+        <v>188</v>
       </c>
       <c r="C11" s="3">
-        <v>4.0</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -6388,13 +5540,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="C12" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6402,13 +5554,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>139</v>
+        <v>299</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6416,13 +5568,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>219</v>
+        <v>147</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6430,10 +5582,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6444,13 +5596,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6470,15 +5622,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>406</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>407</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6492,10 +5644,10 @@
         <v>59</v>
       </c>
       <c r="B3" s="3">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>408</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4">
@@ -6503,10 +5655,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>409</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -6525,7 +5677,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>406</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
@@ -6533,15 +5685,15 @@
         <v>58</v>
       </c>
       <c r="B2" s="3">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6554,23 +5706,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -6578,7 +5730,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>306</v>
+        <v>161</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6586,7 +5738,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6601,8 +5753,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -6613,10 +5765,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>369</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6628,10 +5780,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>412</v>
+        <v>371</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6648,31 +5800,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
@@ -6680,31 +5832,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>415</v>
+        <v>374</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>416</v>
+        <v>375</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="F3" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>80</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4">
@@ -6712,31 +5864,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>288</v>
+        <v>330</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>289</v>
+        <v>184</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="F4" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>420</v>
+        <v>379</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>290</v>
+        <v>332</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
@@ -6744,31 +5896,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>299</v>
+        <v>192</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="F5" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>221</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
@@ -6776,31 +5928,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>423</v>
+        <v>383</v>
       </c>
       <c r="F6" s="3">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>424</v>
+        <v>384</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7">
@@ -6808,31 +5960,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="F7" s="3">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
@@ -6840,31 +5992,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>430</v>
+        <v>310</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>431</v>
+        <v>311</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>174</v>
+        <v>312</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>432</v>
+        <v>376</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>433</v>
+        <v>390</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>434</v>
+        <v>313</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>191</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
@@ -6872,31 +6024,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>421</v>
+        <v>310</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>436</v>
+        <v>314</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -6904,31 +6056,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>73</v>
+        <v>391</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>69</v>
+        <v>392</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>417</v>
+        <v>372</v>
       </c>
       <c r="F10" s="3">
+        <v>57</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -6936,31 +6088,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>438</v>
+        <v>310</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>439</v>
+        <v>395</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>440</v>
+        <v>396</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>44</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -6968,31 +6120,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>316</v>
+        <v>399</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>346</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="F12" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>442</v>
+        <v>400</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -7000,31 +6152,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>287</v>
+        <v>402</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>443</v>
+        <v>311</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>179</v>
+        <v>312</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>444</v>
+        <v>403</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>445</v>
+        <v>404</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>191</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14">
@@ -7032,31 +6184,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>446</v>
+        <v>405</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="F14" s="3">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>448</v>
+        <v>407</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>449</v>
+        <v>408</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15">
@@ -7064,31 +6216,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>450</v>
+        <v>409</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>451</v>
+        <v>151</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>452</v>
+        <v>411</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>453</v>
+        <v>412</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -7096,31 +6248,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>454</v>
+        <v>73</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>455</v>
+        <v>69</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>456</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>457</v>
+        <v>413</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>458</v>
+        <v>75</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>191</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -7128,31 +6280,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>459</v>
+        <v>414</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>179</v>
+        <v>416</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="F17" s="3">
+        <v>44</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="F17" s="3">
-        <v>28</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>461</v>
-      </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>462</v>
+        <v>418</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>463</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18">
@@ -7160,31 +6312,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>464</v>
+        <v>419</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>423</v>
+        <v>383</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>466</v>
+        <v>421</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>467</v>
+        <v>422</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19">
@@ -7192,31 +6344,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>468</v>
+        <v>423</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>469</v>
+        <v>424</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20">
@@ -7224,31 +6376,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>473</v>
+        <v>316</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="F20" s="3">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>474</v>
+        <v>428</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>475</v>
+        <v>429</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
@@ -7256,31 +6408,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>476</v>
+        <v>430</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>477</v>
+        <v>431</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>478</v>
+        <v>432</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>479</v>
+        <v>433</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>121</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W27.xlsx
+++ b/reports/devops-jobs-israel-2026-W27.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="479">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-01T10:06:26</t>
+    <t xml:space="preserve">2026-07-02T09:28:32</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1%</t>
+    <t xml:space="preserve">1.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -159,625 +159,988 @@
     <t xml:space="preserve">Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888525101?gh_jid=4888525101</t>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, CI/CD, Linux, Python, Bash/Shell, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7709743/?gh_jid=7709743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Services DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Services DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Ansible, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4431046130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solution Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888541101?gh_jid=4888541101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, CI/CD, Linux, Python, Bash/Shell, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7709743/?gh_jid=7709743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Services DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Services DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Ansible, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
     <t xml:space="preserve">Devops Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4432560554</t>
+    <t xml:space="preserve">Zafran Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4433814215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-comblack-4434490728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal Recruiting &amp; Placement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-michal-recruiting-placement-4434952736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Modern Workplace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-modern-workplace-at-jobgether-4433676136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4435586069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4431049288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4435550223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4431047248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-25</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4431046130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4436151798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyeviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4431959175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Admin &amp; DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-admin-devops-at-ycon-devops-alm-services-ltd-4431921150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4430658020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINANCIAL INSTITUTION SERVICES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-financial-institution-services-4435534397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudTeam.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4432709751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס/ת DEVOPS ותמיכת תשתיות מחשוב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-devops-%D7%95%D7%AA%D7%9E%D7%99%D7%9B%D7%AA-%D7%AA%D7%A9%D7%AA%D7%99%D7%95%D7%AA-%D7%9E%D7%97%D7%A9%D7%95%D7%91-at-elad-software-systems-4434494489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech Lead – Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tech-lead-%E2%80%93-cloud-devops-engineer-at-maytronics-4434952849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4435564508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer &amp; Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-tech-lead-at-mobileye-4366001366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-workday-4420737999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WINN.AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-winn-ai-4432648338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onyx Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-onyx-security-4433485039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4432394818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4432394657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorious Medical Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4434446138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software AG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4432757303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-sqlink-group-4431082699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SearchApi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-searchapi-4434496090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4434448757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
   </si>
   <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4431091730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4433814215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-comblack-4434490728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michal Recruiting &amp; Placement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-michal-recruiting-placement-4434952736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4435550223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-proteantecs-4432578072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4431047248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4435389030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Admin &amp; DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-admin-devops-at-ycon-devops-alm-services-ltd-4431921150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINN.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-winn-ai-4432648338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vectorious Medical Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4434446138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eyeviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4431959175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4435542128</t>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4434703088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4431039192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-confidential-4434124801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Reliability Engineer MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-audiocodes-4435108288</t>
   </si>
   <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
@@ -792,562 +1155,280 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer - Modern Workplace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-modern-workplace-at-jobgether-4433676136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill Mind Tech Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-skill-mind-tech-bridge-4435107299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4431850858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer | Leading Company (5466)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-leading-company-5466-at-ingima-4434986901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס/ת DEVOPS ותמיכת תשתיות מחשוב</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-devops-%D7%95%D7%AA%D7%9E%D7%99%D7%9B%D7%AA-%D7%AA%D7%A9%D7%AA%D7%99%D7%95%D7%AA-%D7%9E%D7%97%D7%A9%D7%95%D7%91-at-elad-software-systems-4434494489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech Lead – Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tech-lead-%E2%80%93-cloud-devops-engineer-at-maytronics-4434952849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-17</t>
   </si>
   <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (1006913)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-1006913-at-elad-software-systems-4432575125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4434703088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetNut.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Reliability Engineer MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-audiocodes-4435108288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4432603109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior platform engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW DevOps and Test Infrastructure Student, Nitro SW Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Terraform/IaC, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-devops-and-test-infrastructure-student-nitro-sw-team-at-amazon-web-services-aws-4432816876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC &amp; SOC Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-soc-analyst-at-commit-4421804878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4428923734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4422723294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-shavit-software-4426784526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1499,7 +1580,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -1507,7 +1588,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1515,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -1523,7 +1604,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>813</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10">
@@ -1595,7 +1676,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -1603,7 +1684,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1622,39 +1703,47 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>383</v>
+        <v>461</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1670,63 +1759,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>355</v>
+        <v>390</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
@@ -1734,55 +1823,55 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>358</v>
+        <v>468</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>441</v>
+        <v>385</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>353</v>
+        <v>469</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>442</v>
+        <v>384</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -1790,7 +1879,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -1818,13 +1907,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>445</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2">
@@ -1832,13 +1921,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1847,88 +1936,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
-        <v>57.1</v>
+        <v>33.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.0</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>1.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>28.9</v>
+        <v>34.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.0</v>
+        <v>19.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>13.9</v>
+        <v>16.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1939,9 +2028,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2012,7 +2101,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -2044,7 +2133,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -2073,15 +2162,15 @@
         <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>35</v>
@@ -2096,115 +2185,115 @@
         <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J6" s="3">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -2212,252 +2301,252 @@
         <v>63</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="J10" s="3">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J12" s="3">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="J15" s="3">
-        <v>50</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J16" s="3">
         <v>21</v>
@@ -2465,693 +2554,689 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J17" s="3">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J18" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="J19" s="3">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="J20" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J21" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J23" s="3">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="J26" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="J29" s="3">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>153</v>
-      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J31" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="J33" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>166</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="J34" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="J36" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="J38" s="3">
         <v>2</v>
@@ -3159,139 +3244,139 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>187</v>
+        <v>128</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>48</v>
+        <v>194</v>
       </c>
       <c r="J40" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="J41" s="3">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="J42" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>199</v>
+        <v>58</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3301,121 +3386,119 @@
         <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>63</v>
+        <v>206</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>213</v>
+        <v>128</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
@@ -3423,24 +3506,24 @@
         <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>38</v>
@@ -3450,87 +3533,89 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="J48" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>122</v>
+        <v>222</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>225</v>
+        <v>53</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F50" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>225</v>
+        <v>53</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3540,57 +3625,57 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="J51" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>63</v>
+        <v>235</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>38</v>
@@ -3600,130 +3685,130 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>188</v>
+        <v>239</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>210</v>
+        <v>134</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="J54" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>182</v>
+        <v>245</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>63</v>
+        <v>206</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -3731,149 +3816,151 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="J58" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>251</v>
+        <v>181</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>58</v>
+        <v>212</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>255</v>
+        <v>54</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="J61" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="J62" s="3">
         <v>2</v>
@@ -3881,89 +3968,89 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>122</v>
+        <v>265</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>262</v>
+        <v>58</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>182</v>
+        <v>270</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>188</v>
+        <v>272</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>76</v>
+        <v>274</v>
       </c>
       <c r="J65" s="3">
         <v>43</v>
@@ -3971,695 +4058,691 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>270</v>
+        <v>44</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>56</v>
+        <v>278</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>172</v>
+        <v>274</v>
       </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="J68" s="3">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J70" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="J71" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>70</v>
+        <v>296</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="J72" s="3">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>292</v>
+        <v>150</v>
       </c>
       <c r="J73" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>122</v>
+        <v>301</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>294</v>
+        <v>173</v>
       </c>
       <c r="J74" s="3">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>90</v>
+        <v>304</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>297</v>
+        <v>205</v>
       </c>
       <c r="J75" s="3">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>186</v>
+        <v>71</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>305</v>
+        <v>245</v>
       </c>
       <c r="J77" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="J78" s="3">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="J79" s="3">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>182</v>
+        <v>245</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>173</v>
+        <v>320</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>174</v>
+        <v>321</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>285</v>
+        <v>96</v>
       </c>
       <c r="J82" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>318</v>
+        <v>128</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>201</v>
+        <v>326</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>320</v>
+        <v>63</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="J84" s="3">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>322</v>
+        <v>128</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>248</v>
+        <v>171</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>325</v>
+        <v>173</v>
       </c>
       <c r="J85" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="D86" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I86" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J86" s="3">
         <v>44</v>
-      </c>
-      <c r="J86" s="3">
-        <v>47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>184</v>
+        <v>321</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>331</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="J87" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>333</v>
+        <v>128</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4667,76 +4750,78 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F89" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="J89" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>342</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>343</v>
+        <v>134</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="J90" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>346</v>
-      </c>
       <c r="C91" s="3" t="s">
-        <v>248</v>
+        <v>199</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>38</v>
@@ -4746,17 +4831,349 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J91" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J91" s="3">
-        <v>27</v>
+      <c r="C92" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J92" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="J93" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="J94" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J95" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="J96" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J98" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J99" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J100" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J101" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J102" s="3">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J91"/>
+  <autoFilter ref="A1:J102"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4848,6 +5265,17 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4855,9 +5283,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4889,13 +5317,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4903,18 +5331,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4922,18 +5350,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4941,18 +5369,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>231</v>
+        <v>171</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4960,18 +5388,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4979,18 +5407,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>63</v>
+        <v>304</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4998,18 +5426,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>242</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>251</v>
+        <v>321</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5017,18 +5445,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>252</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>204</v>
+        <v>326</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5036,18 +5464,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>261</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>277</v>
+        <v>128</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>201</v>
+        <v>336</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5055,18 +5483,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>279</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5074,11 +5502,30 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5090,6 +5537,7 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5103,55 +5551,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>350</v>
+        <v>227</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5159,7 +5607,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>331</v>
+        <v>386</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -5167,15 +5615,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5183,7 +5631,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5191,7 +5639,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5199,31 +5647,31 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5236,7 +5684,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5245,28 +5693,28 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5274,15 +5722,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>188</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5290,15 +5738,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5306,7 +5754,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5314,7 +5762,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5322,7 +5770,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5330,7 +5778,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5338,7 +5786,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5346,7 +5794,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>281</v>
+        <v>185</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5354,7 +5802,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>290</v>
+        <v>192</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5362,7 +5810,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5376,23 +5824,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
@@ -5400,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C2" s="3">
         <v>19.2</v>
@@ -5414,13 +5862,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>17.3</v>
+        <v>15.1</v>
       </c>
       <c r="D3" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -5428,10 +5876,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
-        <v>15.1</v>
+        <v>12.5</v>
       </c>
       <c r="D4" s="3">
         <v>4</v>
@@ -5442,7 +5890,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C5" s="3">
         <v>10.9</v>
@@ -5456,7 +5904,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C6" s="3">
         <v>7.3</v>
@@ -5470,10 +5918,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C7" s="3">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5484,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
@@ -5498,13 +5946,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -5512,10 +5960,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -5526,13 +5974,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5540,13 +5988,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>134</v>
+        <v>320</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5554,13 +6002,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>299</v>
+        <v>129</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5568,13 +6016,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5582,10 +6030,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -5596,13 +6044,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5622,15 +6070,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>255</v>
+        <v>376</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -5641,13 +6089,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>367</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4">
@@ -5655,10 +6103,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -5677,23 +6125,23 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -5706,7 +6154,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -5714,33 +6162,25 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>225</v>
+        <v>156</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5753,8 +6193,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -5765,10 +6205,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5780,10 +6220,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5800,31 +6240,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>253</v>
+        <v>374</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>254</v>
+        <v>375</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>256</v>
+        <v>377</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -5832,31 +6272,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>375</v>
+        <v>295</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>70</v>
+        <v>296</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>297</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4">
@@ -5864,31 +6304,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>329</v>
+        <v>411</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>330</v>
+        <v>412</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>332</v>
+        <v>415</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>186</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
@@ -5896,31 +6336,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>192</v>
+        <v>354</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>380</v>
+        <v>416</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6">
@@ -5928,31 +6368,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="F6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
@@ -5960,31 +6400,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="F7" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8">
@@ -5992,31 +6432,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>310</v>
+        <v>421</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>311</v>
+        <v>422</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="F8" s="3">
         <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>313</v>
+        <v>424</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9">
@@ -6024,31 +6464,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="F9" s="3">
         <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>314</v>
+        <v>426</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>270</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -6056,31 +6496,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>391</v>
+        <v>333</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>392</v>
+        <v>320</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>192</v>
+        <v>321</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>372</v>
+        <v>413</v>
       </c>
       <c r="F10" s="3">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>394</v>
+        <v>334</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>44</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6088,31 +6528,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>310</v>
+        <v>427</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="F11" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6120,31 +6560,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>398</v>
+        <v>333</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13">
@@ -6152,31 +6592,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="F13" s="3">
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>305</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14">
@@ -6184,31 +6624,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>408</v>
+        <v>441</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
@@ -6216,31 +6656,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>151</v>
+        <v>443</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>152</v>
+        <v>444</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>44</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16">
@@ -6248,31 +6688,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>73</v>
+        <v>442</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>413</v>
+        <v>448</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>75</v>
+        <v>449</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -6280,31 +6720,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>416</v>
+        <v>181</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>101</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18">
@@ -6312,31 +6752,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>419</v>
+        <v>68</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>420</v>
+        <v>64</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="F18" s="3">
         <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>422</v>
+        <v>70</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>186</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
@@ -6344,31 +6784,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>424</v>
+        <v>347</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="F19" s="3">
         <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>186</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -6376,31 +6816,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>316</v>
+        <v>457</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="F20" s="3">
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
@@ -6408,31 +6848,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>430</v>
+        <v>341</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>431</v>
+        <v>339</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>224</v>
+        <v>342</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="F21" s="3">
         <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>433</v>
+        <v>343</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>276</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W27.xlsx
+++ b/reports/devops-jobs-israel-2026-W27.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-02T09:28:32</t>
+    <t xml:space="preserve">2026-07-03T09:31:27</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,15 +57,12 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0%</t>
+    <t xml:space="preserve">0.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0%</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -351,7 +348,7 @@
     <t xml:space="preserve">Tel Aviv, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, Ansible, Linux, Kafka, Airflow, dbt, Spark</t>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
@@ -510,133 +507,571 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4431046130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4432791201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433127155</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4434379427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4435550223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4435564508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4431047248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435227245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4435586069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorious Medical Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4434446138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onyx Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-onyx-security-4433485039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס/ת DEVOPS ותמיכת תשתיות מחשוב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-devops-%D7%95%D7%AA%D7%9E%D7%99%D7%9B%D7%AA-%D7%AA%D7%A9%D7%AA%D7%99%D7%95%D7%AA-%D7%9E%D7%97%D7%A9%D7%95%D7%91-at-elad-software-systems-4434494489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4434293341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Consultant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elsight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-consultant-at-elsight-4434363102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-and-automation-engineer-at-nvidia-4435289176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4432394818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-comblack-4436344599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director, DOCA DevOps and Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-doca-devops-and-integration-at-nvidia-ai-4430633617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stampli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427522493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Reliability Engineer MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-audiocodes-4435108288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4432394657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Modern Workplace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-modern-workplace-at-jobgether-4433676136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration &amp; DevOps Engineer (Kubernetes / OpenShift)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-devops-engineer-kubernetes-openshift-at-commit-4435574441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudTeam.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4432709751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-varonis-4435128191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4432713200</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4431046130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4433814215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-comblack-4434490728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michal Recruiting &amp; Placement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-michal-recruiting-placement-4434952736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Modern Workplace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-modern-workplace-at-jobgether-4433676136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4435586069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-confidential-careers-4431040388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-sqlink-group-4431082699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-camtek-4432761684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturing Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manufacturing-infrastructure-engineer-at-quantum-machines-4434304423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4431039192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPS-JOBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-sps-jobs-4431035610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-confidential-4434124801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Specialist</t>
@@ -651,430 +1086,184 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4431049288</t>
   </si>
   <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4435550223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4431047248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4433081626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4436151798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eyeviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4431959175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Admin &amp; DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-admin-devops-at-ycon-devops-alm-services-ltd-4431921150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4431060955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech Lead – Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tech-lead-%E2%80%93-cloud-devops-engineer-at-maytronics-4434952849</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4430658020</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINANCIAL INSTITUTION SERVICES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-financial-institution-services-4435534397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudTeam.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4432709751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס/ת DEVOPS ותמיכת תשתיות מחשוב</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-devops-%D7%95%D7%AA%D7%9E%D7%99%D7%9B%D7%AA-%D7%AA%D7%A9%D7%AA%D7%99%D7%95%D7%AA-%D7%9E%D7%97%D7%A9%D7%95%D7%91-at-elad-software-systems-4434494489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech Lead – Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tech-lead-%E2%80%93-cloud-devops-engineer-at-maytronics-4434952849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4435564508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer &amp; Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
   </si>
   <si>
     <t xml:space="preserve">Jerusalem District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-tech-lead-at-mobileye-4366001366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-workday-4420737999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINN.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-winn-ai-4432648338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onyx Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-onyx-security-4433485039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4432394818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4432394657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vectorious Medical Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4434446138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software AG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4432757303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-sqlink-group-4431082699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SearchApi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-searchapi-4434496090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4434448757</t>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
   </si>
   <si>
     <t xml:space="preserve">Linux System Engineer</t>
@@ -1083,199 +1272,25 @@
     <t xml:space="preserve">Calanit by one</t>
   </si>
   <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
   </si>
   <si>
-    <t xml:space="preserve">Integration Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4434703088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetNut.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4431039192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-confidential-4434124801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Reliability Engineer MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-audiocodes-4435108288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
   </si>
   <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
@@ -1284,6 +1299,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI Inclined Systems Engineer</t>
   </si>
   <si>
@@ -1296,10 +1317,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+    <t xml:space="preserve">Technical Support Engineer 241123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-241123-at-experis-israel-4432336498</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
@@ -1314,13 +1341,28 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
@@ -1329,6 +1371,9 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
   </si>
   <si>
@@ -1356,9 +1401,6 @@
     <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1380,33 +1422,6 @@
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1416,13 +1431,13 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1580,7 +1595,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7">
@@ -1588,7 +1603,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1596,7 +1611,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -1604,7 +1619,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>824</v>
+        <v>838</v>
       </c>
     </row>
     <row r="10">
@@ -1612,7 +1627,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1628,7 +1643,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1637,26 +1652,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1665,23 +1680,23 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="3">
         <v>31</v>
@@ -1700,39 +1715,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="B2" s="3">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1740,7 +1755,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1759,71 +1774,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>464</v>
+        <v>358</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>355</v>
+        <v>470</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>467</v>
+        <v>382</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>389</v>
+        <v>472</v>
       </c>
       <c r="B9" s="3">
         <v>18</v>
@@ -1831,55 +1846,55 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -1901,123 +1916,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3">
         <v>31</v>
       </c>
       <c r="C2" s="3">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3">
-        <v>33.9</v>
+        <v>35.5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.2</v>
+        <v>35.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.5</v>
+        <v>16.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2030,7 +2045,7 @@
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2042,1149 +2057,1149 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J2" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J3" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="C6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="J6" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J7" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J8" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="J10" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="J12" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="I13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J13" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="J14" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="J15" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J16" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="J17" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I18" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J18" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="I19" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J19" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="J20" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="J21" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J22" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="J23" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J24" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J25" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J26" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="I27" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J27" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="I28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J28" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="J29" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="I30" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J30" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="J31" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="I32" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J32" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="J33" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J34" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J35" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J36" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>180</v>
@@ -3193,230 +3208,230 @@
         <v>181</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="J37" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J38" s="3">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="J39" s="3">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="J40" s="3">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="J41" s="3">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="J42" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -3424,59 +3439,59 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>206</v>
+        <v>62</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>212</v>
+        <v>52</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="J46" s="3">
         <v>1</v>
@@ -3484,331 +3499,329 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="J47" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>218</v>
+        <v>163</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>219</v>
+        <v>52</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="J48" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>222</v>
+        <v>57</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>219</v>
+        <v>52</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>205</v>
+        <v>95</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>227</v>
-      </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>231</v>
+        <v>57</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="J53" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>128</v>
+        <v>229</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>58</v>
+        <v>235</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>181</v>
+        <v>237</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="J56" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -3816,421 +3829,421 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>248</v>
+        <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>250</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>254</v>
+        <v>175</v>
       </c>
       <c r="J59" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>85</v>
+        <v>247</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>257</v>
+        <v>175</v>
       </c>
       <c r="J60" s="3">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>212</v>
+        <v>52</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>188</v>
+        <v>136</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>263</v>
+        <v>178</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>188</v>
+        <v>254</v>
       </c>
       <c r="J62" s="3">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="J63" s="3">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>58</v>
+        <v>259</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>268</v>
+        <v>201</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="J64" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>272</v>
+        <v>180</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>181</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>274</v>
+        <v>70</v>
       </c>
       <c r="J65" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="J66" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>279</v>
+        <v>241</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>280</v>
+        <v>181</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>274</v>
+        <v>198</v>
       </c>
       <c r="J67" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="D68" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>285</v>
+        <v>165</v>
       </c>
       <c r="J68" s="3">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J69" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="D70" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="J70" s="3">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>128</v>
+        <v>278</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>186</v>
+        <v>275</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>134</v>
+        <v>276</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F71" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="G71" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="J71" s="3">
         <v>0</v>
@@ -4238,121 +4251,121 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="J72" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>298</v>
+        <v>57</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="J73" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D74" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="G74" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>171</v>
+        <v>64</v>
       </c>
       <c r="D75" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E75" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>306</v>
-      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="J75" s="3">
         <v>0</v>
@@ -4360,820 +4373,884 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>309</v>
+        <v>178</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>212</v>
+        <v>52</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>71</v>
+        <v>296</v>
       </c>
       <c r="J76" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>128</v>
+        <v>297</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>313</v>
+        <v>180</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>167</v>
+        <v>299</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="J78" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="J79" s="3">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>245</v>
+        <v>190</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>58</v>
+        <v>306</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>321</v>
+        <v>163</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F81" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>308</v>
+      </c>
       <c r="G81" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J82" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>128</v>
+        <v>313</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>205</v>
+        <v>70</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>63</v>
+        <v>306</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>175</v>
+        <v>315</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>309</v>
+        <v>163</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>212</v>
+        <v>52</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F84" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>308</v>
+      </c>
       <c r="G84" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>71</v>
+        <v>228</v>
       </c>
       <c r="J84" s="3">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>326</v>
+        <v>204</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J86" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>321</v>
+        <v>178</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>173</v>
+        <v>324</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>128</v>
+        <v>321</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>339</v>
+        <v>241</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="D89" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>227</v>
-      </c>
+      <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>342</v>
+        <v>163</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F90" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>331</v>
+      </c>
       <c r="G90" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>199</v>
+        <v>334</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D92" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="J92" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="J93" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>353</v>
+        <v>167</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>355</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>183</v>
+        <v>254</v>
       </c>
       <c r="J94" s="3">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>185</v>
+        <v>345</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="J96" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>363</v>
+        <v>196</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>175</v>
+        <v>352</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D98" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>257</v>
+        <v>165</v>
       </c>
       <c r="J98" s="3">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>186</v>
+        <v>357</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F99" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>358</v>
+      </c>
       <c r="G99" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="J99" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>372</v>
+        <v>178</v>
       </c>
       <c r="D100" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>214</v>
+        <v>363</v>
       </c>
       <c r="J100" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>65</v>
+        <v>217</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>376</v>
+        <v>37</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J101" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="J102" s="3">
-        <v>28</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J103" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J104" s="3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J102"/>
+  <autoFilter ref="A1:J104"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5276,6 +5353,8 @@
     <hyperlink ref="H100" r:id="rId99"/>
     <hyperlink ref="H101" r:id="rId100"/>
     <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5283,9 +5362,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5294,238 +5373,295 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>206</v>
+        <v>127</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>247</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>248</v>
+        <v>127</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>249</v>
+        <v>201</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>293</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>304</v>
+        <v>239</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>305</v>
+        <v>180</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>307</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>320</v>
+        <v>244</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>321</v>
+        <v>245</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>128</v>
+        <v>247</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>320</v>
+        <v>241</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>326</v>
+        <v>242</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>327</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>128</v>
+        <v>263</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>335</v>
+        <v>264</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>336</v>
+        <v>178</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>337</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>341</v>
+        <v>278</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>339</v>
+        <v>279</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>342</v>
+        <v>275</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>343</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>341</v>
+        <v>273</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>362</v>
+        <v>292</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>363</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>364</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5538,6 +5674,9 @@
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5551,15 +5690,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -5567,7 +5706,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>227</v>
+        <v>308</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5575,7 +5714,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5583,15 +5722,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5599,7 +5738,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5607,7 +5746,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -5615,7 +5754,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5623,7 +5762,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5631,7 +5770,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5639,7 +5778,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5647,7 +5786,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5655,7 +5794,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5663,7 +5802,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5671,7 +5810,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5690,15 +5829,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5706,15 +5845,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5722,7 +5861,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -5730,31 +5869,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5762,7 +5901,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5770,7 +5909,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5778,7 +5917,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5786,7 +5925,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5794,7 +5933,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5810,7 +5949,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5831,16 +5970,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
@@ -5848,7 +5987,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3">
         <v>19.2</v>
@@ -5862,7 +6001,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3">
         <v>15.1</v>
@@ -5876,7 +6015,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
         <v>12.5</v>
@@ -5890,7 +6029,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="3">
         <v>10.9</v>
@@ -5904,7 +6043,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="3">
         <v>7.3</v>
@@ -5918,13 +6057,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>118</v>
+        <v>241</v>
       </c>
       <c r="C7" s="3">
-        <v>5.3</v>
+        <v>7.0</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -5932,13 +6071,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>5.6</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -5946,13 +6085,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="C9" s="3">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5960,10 +6099,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3">
-        <v>4.6</v>
+        <v>5.0</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -5974,13 +6113,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="C11" s="3">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -5988,13 +6127,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>320</v>
+        <v>63</v>
       </c>
       <c r="C12" s="3">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6002,13 +6141,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6016,13 +6155,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6030,7 +6169,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -6044,7 +6183,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -6067,46 +6206,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -6122,63 +6261,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="3">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>156</v>
+        <v>276</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>124</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6205,34 +6344,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6240,31 +6379,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>375</v>
+        <v>274</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>65</v>
+        <v>400</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>80</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3">
@@ -6272,13 +6411,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>296</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>407</v>
@@ -6290,13 +6429,13 @@
         <v>408</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>409</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>410</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -6304,31 +6443,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>413</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>415</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
@@ -6336,31 +6475,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>352</v>
+        <v>415</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>354</v>
+        <v>245</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>356</v>
+        <v>418</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6">
@@ -6368,31 +6507,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>341</v>
+        <v>419</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>347</v>
+        <v>420</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>348</v>
+        <v>423</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7">
@@ -6400,31 +6539,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>352</v>
+        <v>415</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>418</v>
+        <v>171</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F7" s="3">
         <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
@@ -6432,31 +6571,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>421</v>
+        <v>327</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>422</v>
+        <v>241</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F8" s="3">
         <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>424</v>
+        <v>328</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>238</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
@@ -6464,31 +6603,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>164</v>
+        <v>299</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F9" s="3">
         <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -6496,31 +6635,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>333</v>
+        <v>428</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>320</v>
+        <v>429</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>321</v>
+        <v>178</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F10" s="3">
         <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>334</v>
+        <v>431</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -6528,31 +6667,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>181</v>
+        <v>342</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>44</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6560,31 +6699,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>333</v>
+        <v>436</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="F12" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -6592,31 +6731,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>437</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14">
@@ -6624,31 +6763,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15">
@@ -6656,31 +6795,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>443</v>
+        <v>180</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>444</v>
+        <v>299</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="F15" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16">
@@ -6688,31 +6827,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>146</v>
+        <v>241</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>147</v>
+        <v>242</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>44</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17">
@@ -6720,31 +6859,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18">
@@ -6752,31 +6891,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>68</v>
+        <v>457</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>458</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>65</v>
+        <v>459</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>70</v>
+        <v>461</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>71</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19">
@@ -6784,31 +6923,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>347</v>
+        <v>145</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -6816,31 +6955,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>93</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21">
@@ -6848,31 +6987,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>341</v>
+        <v>67</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>339</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>342</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>343</v>
+        <v>69</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>214</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W27.xlsx
+++ b/reports/devops-jobs-israel-2026-W27.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="479">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-03T09:31:27</t>
+    <t xml:space="preserve">2026-07-05T09:19:14</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -402,6 +402,18 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Engineer - Billing Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python, Postgres, Redis, Kafka, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
@@ -432,15 +444,6 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Data Infra Engineer</t>
   </si>
   <si>
@@ -507,937 +510,919 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4425548689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4432394657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration &amp; DevOps Engineer (Kubernetes / OpenShift)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-devops-engineer-kubernetes-openshift-at-commit-4435574441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MatchPointIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matchpointit-4433773859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433127155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4433787217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435244149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorious Medical Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4434446138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4431049288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudTeam.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4432709751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matchpointit-4436991278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-comblack-4436344599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4433900010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4433773897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4435778756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4431047248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4435550223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4432791201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4436979806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4431046130</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+    <t xml:space="preserve">AI Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4432713200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-confidential-careers-4431040388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINANCIAL INSTITUTION SERVICES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-financial-institution-services-4435534397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4432325499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4432791201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433127155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4434379427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4435550223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-camtek-4432761684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspect Imaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-aspect-imaging-4434489230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturing Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manufacturing-infrastructure-engineer-at-quantum-machines-4434304423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4431039192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-confidential-4434124801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPS-JOBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-sps-jobs-4431035610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - Naval Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-naval-systems-at-elbit-systems-israel-4423104948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-sqlink-group-4431082699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Reliability Engineer MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-audiocodes-4435108288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4435564508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4431047248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435227245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4435586069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vectorious Medical Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4434446138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4434407348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onyx Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-onyx-security-4433485039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס/ת DEVOPS ותמיכת תשתיות מחשוב</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-devops-%D7%95%D7%AA%D7%9E%D7%99%D7%9B%D7%AA-%D7%AA%D7%A9%D7%AA%D7%99%D7%95%D7%AA-%D7%9E%D7%97%D7%A9%D7%95%D7%91-at-elad-software-systems-4434494489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4434293341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Consultant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elsight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-consultant-at-elsight-4434363102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-and-automation-engineer-at-nvidia-4435289176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4432394818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-comblack-4436344599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director, DOCA DevOps and Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-doca-devops-and-integration-at-nvidia-ai-4430633617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stampli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427522493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Reliability Engineer MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-audiocodes-4435108288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4432394657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Modern Workplace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-modern-workplace-at-jobgether-4433676136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infra-engineer-at-scaleops-4434282728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration &amp; DevOps Engineer (Kubernetes / OpenShift)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-devops-engineer-kubernetes-openshift-at-commit-4435574441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-autobrains-technologies-4433611495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudTeam.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4432709751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-varonis-4435128191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4432713200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-confidential-careers-4431040388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-sqlink-group-4431082699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
   </si>
   <si>
     <t xml:space="preserve">Paragon</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
   </si>
   <si>
     <t xml:space="preserve">Ashdod, South District, Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-camtek-4432761684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufacturing Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manufacturing-infrastructure-engineer-at-quantum-machines-4434304423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4431039192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPS-JOBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-sps-jobs-4431035610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-confidential-4434124801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4431049288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4431060955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetNut.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech Lead – Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tech-lead-%E2%80%93-cloud-devops-engineer-at-maytronics-4434952849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4430658020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer 241123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-241123-at-experis-israel-4432336498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyHeritage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-myheritage-4434704007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1595,7 +1580,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7">
@@ -1611,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -1619,7 +1604,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>838</v>
+        <v>852</v>
       </c>
     </row>
     <row r="10">
@@ -1691,7 +1676,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1718,36 +1703,36 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1755,7 +1740,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1774,103 +1759,103 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B2" s="3">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="B3" s="3">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>358</v>
+        <v>464</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>472</v>
+        <v>369</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>473</v>
+        <v>366</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>378</v>
+        <v>468</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -1878,26 +1863,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>280</v>
+        <v>173</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1922,13 +1907,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2">
@@ -1939,10 +1924,10 @@
         <v>31</v>
       </c>
       <c r="C2" s="3">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1951,88 +1936,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
-        <v>35.5</v>
+        <v>42.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.2</v>
+        <v>31.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.0</v>
+        <v>15.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2116,7 +2101,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -2148,7 +2133,7 @@
         <v>43</v>
       </c>
       <c r="J3" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -2180,7 +2165,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2197,7 @@
         <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -2244,7 +2229,7 @@
         <v>56</v>
       </c>
       <c r="J6" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -2276,7 +2261,7 @@
         <v>40</v>
       </c>
       <c r="J7" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
@@ -2308,7 +2293,7 @@
         <v>40</v>
       </c>
       <c r="J8" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -2340,7 +2325,7 @@
         <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -2372,7 +2357,7 @@
         <v>70</v>
       </c>
       <c r="J10" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -2404,7 +2389,7 @@
         <v>40</v>
       </c>
       <c r="J11" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -2436,7 +2421,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -2468,7 +2453,7 @@
         <v>40</v>
       </c>
       <c r="J13" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2500,7 +2485,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -2532,7 +2517,7 @@
         <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -2564,7 +2549,7 @@
         <v>95</v>
       </c>
       <c r="J16" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2596,7 +2581,7 @@
         <v>99</v>
       </c>
       <c r="J17" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -2628,7 +2613,7 @@
         <v>92</v>
       </c>
       <c r="J18" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -2660,7 +2645,7 @@
         <v>43</v>
       </c>
       <c r="J19" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -2692,7 +2677,7 @@
         <v>111</v>
       </c>
       <c r="J20" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2724,7 +2709,7 @@
         <v>115</v>
       </c>
       <c r="J21" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
@@ -2756,7 +2741,7 @@
         <v>99</v>
       </c>
       <c r="J22" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -2788,7 +2773,7 @@
         <v>122</v>
       </c>
       <c r="J23" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -2820,7 +2805,7 @@
         <v>40</v>
       </c>
       <c r="J24" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
@@ -2828,80 +2813,80 @@
         <v>127</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J25" s="3">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="J26" s="3">
-        <v>21</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>138</v>
@@ -2913,18 +2898,18 @@
         <v>139</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="J27" s="3">
-        <v>52</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>108</v>
@@ -2936,30 +2921,30 @@
         <v>37</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J28" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>52</v>
@@ -2968,30 +2953,30 @@
         <v>37</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J29" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>52</v>
@@ -3000,33 +2985,33 @@
         <v>37</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J30" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>37</v>
@@ -3036,21 +3021,21 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J31" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>52</v>
@@ -3062,33 +3047,33 @@
         <v>37</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J32" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>53</v>
@@ -3098,27 +3083,27 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="J33" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>53</v>
@@ -3128,32 +3113,34 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J34" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F35" s="3"/>
+      <c r="F35" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
@@ -3164,18 +3151,18 @@
         <v>175</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>52</v>
@@ -3188,10 +3175,10 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="J36" s="3">
         <v>0</v>
@@ -3199,7 +3186,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>180</v>
@@ -3208,7 +3195,7 @@
         <v>181</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>53</v>
@@ -3224,24 +3211,24 @@
         <v>175</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
@@ -3251,21 +3238,21 @@
         <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="J38" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>52</v>
@@ -3281,27 +3268,27 @@
         <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J39" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>173</v>
+        <v>52</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
@@ -3314,21 +3301,21 @@
         <v>190</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>53</v>
@@ -3338,27 +3325,27 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>194</v>
+        <v>70</v>
       </c>
       <c r="J41" s="3">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>53</v>
@@ -3368,30 +3355,30 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>127</v>
+        <v>198</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3401,27 +3388,27 @@
         <v>200</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="J43" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -3431,24 +3418,24 @@
         <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>53</v>
@@ -3458,27 +3445,27 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>70</v>
+        <v>197</v>
       </c>
       <c r="J45" s="3">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>53</v>
@@ -3488,147 +3475,149 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>127</v>
+        <v>211</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="J47" s="3">
-        <v>4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="J48" s="3">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>95</v>
+        <v>218</v>
       </c>
       <c r="J49" s="3">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F50" s="3"/>
+      <c r="F50" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>219</v>
+        <v>131</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>53</v>
@@ -3638,84 +3627,84 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J51" s="3">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="J52" s="3">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>225</v>
+        <v>57</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>173</v>
+        <v>52</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>229</v>
+        <v>57</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>230</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>52</v>
@@ -3731,21 +3720,21 @@
         <v>231</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="J54" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>52</v>
@@ -3758,24 +3747,24 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J55" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>235</v>
+        <v>57</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>236</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>52</v>
@@ -3788,13 +3777,13 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
@@ -3802,10 +3791,10 @@
         <v>239</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>52</v>
@@ -3818,27 +3807,27 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>57</v>
+        <v>243</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>37</v>
@@ -3848,13 +3837,13 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3862,13 +3851,13 @@
         <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>37</v>
@@ -3881,7 +3870,7 @@
         <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
@@ -3892,13 +3881,13 @@
         <v>247</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>53</v>
@@ -3908,117 +3897,117 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>249</v>
+        <v>57</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>178</v>
+        <v>252</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="J61" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>84</v>
+        <v>254</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="J62" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>163</v>
+        <v>260</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>52</v>
+        <v>261</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>258</v>
+        <v>130</v>
       </c>
       <c r="J63" s="3">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>201</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>52</v>
+        <v>172</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>53</v>
@@ -4028,27 +4017,27 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
@@ -4058,10 +4047,10 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>70</v>
+        <v>238</v>
       </c>
       <c r="J65" s="3">
         <v>45</v>
@@ -4069,13 +4058,13 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>52</v>
@@ -4088,27 +4077,27 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>175</v>
+        <v>271</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>127</v>
+        <v>272</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>53</v>
@@ -4118,27 +4107,27 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>267</v>
+        <v>131</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>53</v>
@@ -4148,211 +4137,209 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>165</v>
+        <v>277</v>
       </c>
       <c r="J68" s="3">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J69" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>275</v>
+        <v>177</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>276</v>
+        <v>52</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F70" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="J70" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>278</v>
+        <v>131</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>275</v>
+        <v>177</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>276</v>
+        <v>52</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>280</v>
-      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>284</v>
+        <v>181</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J72" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>286</v>
+        <v>216</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>288</v>
+        <v>131</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>163</v>
+        <v>292</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>290</v>
-      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>273</v>
+        <v>131</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="D75" s="3" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>53</v>
@@ -4362,24 +4349,24 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>175</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>183</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>178</v>
+        <v>298</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>52</v>
@@ -4392,70 +4379,70 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>296</v>
+        <v>43</v>
       </c>
       <c r="J76" s="3">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>242</v>
+        <v>171</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>297</v>
+        <v>131</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>180</v>
+        <v>303</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>299</v>
+        <v>256</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="J78" s="3">
         <v>0</v>
@@ -4463,73 +4450,73 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>302</v>
+        <v>163</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>178</v>
+        <v>306</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="J79" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>52</v>
@@ -4537,34 +4524,32 @@
       <c r="E81" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>308</v>
-      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>311</v>
+        <v>166</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>178</v>
+        <v>312</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>37</v>
@@ -4574,24 +4559,24 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="J82" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>313</v>
+        <v>131</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>52</v>
@@ -4604,24 +4589,24 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="J83" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>52</v>
@@ -4630,63 +4615,63 @@
         <v>53</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="J84" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>57</v>
+        <v>207</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="J85" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>167</v>
+        <v>323</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>204</v>
+        <v>324</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>53</v>
@@ -4696,57 +4681,57 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="J86" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>322</v>
+        <v>163</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>324</v>
+        <v>238</v>
       </c>
       <c r="J87" s="3">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>325</v>
+        <v>256</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>53</v>
@@ -4756,27 +4741,27 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>241</v>
+        <v>332</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>242</v>
+        <v>333</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>53</v>
@@ -4786,86 +4771,84 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>165</v>
+        <v>335</v>
       </c>
       <c r="J89" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>163</v>
+        <v>324</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>331</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>175</v>
+        <v>341</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>52</v>
@@ -4878,27 +4861,27 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>228</v>
+        <v>70</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>53</v>
@@ -4908,24 +4891,24 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="I93" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="I93" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>52</v>
@@ -4938,40 +4921,40 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="J94" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>196</v>
+        <v>351</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="J95" s="3">
         <v>3</v>
@@ -4979,16 +4962,16 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>347</v>
+        <v>279</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>37</v>
@@ -4998,57 +4981,57 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>228</v>
+        <v>341</v>
       </c>
       <c r="J96" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>165</v>
+        <v>341</v>
       </c>
       <c r="J97" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>352</v>
+        <v>191</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>353</v>
+        <v>192</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>53</v>
@@ -5058,33 +5041,33 @@
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="J98" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>357</v>
+        <v>177</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>22</v>
@@ -5093,10 +5076,10 @@
         <v>359</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>165</v>
+        <v>341</v>
       </c>
       <c r="J99" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -5104,10 +5087,10 @@
         <v>360</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>361</v>
+        <v>185</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>52</v>
@@ -5120,137 +5103,17 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>363</v>
+        <v>190</v>
       </c>
       <c r="J100" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J101" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="J102" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J103" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J104" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J104"/>
+  <autoFilter ref="A1:J100"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5351,10 +5214,6 @@
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
     <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
-    <hyperlink ref="H103" r:id="rId102"/>
-    <hyperlink ref="H104" r:id="rId103"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5362,8 +5221,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5399,29 +5258,29 @@
         <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5429,18 +5288,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5448,18 +5307,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>202</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5467,18 +5326,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5486,18 +5345,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>180</v>
+        <v>244</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5505,7 +5364,7 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
@@ -5513,10 +5372,10 @@
         <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5529,13 +5388,13 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5543,18 +5402,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>178</v>
+        <v>260</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5562,18 +5421,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>275</v>
+        <v>171</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5581,18 +5440,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>273</v>
+        <v>131</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5600,18 +5459,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>241</v>
+        <v>323</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>242</v>
+        <v>324</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5619,18 +5478,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>180</v>
+        <v>329</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>299</v>
+        <v>256</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5638,18 +5497,18 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>321</v>
+        <v>356</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>333</v>
+        <v>191</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>334</v>
+        <v>192</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5657,7 +5516,7 @@
         <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -5690,15 +5549,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -5706,7 +5565,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5714,7 +5573,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5722,15 +5581,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>280</v>
+        <v>173</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5738,7 +5597,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>160</v>
+        <v>367</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5746,23 +5605,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>379</v>
+        <v>161</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5770,7 +5629,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5778,7 +5637,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5786,7 +5645,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5794,7 +5653,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5802,7 +5661,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5810,10 +5669,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5823,7 +5682,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5832,7 +5691,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -5845,7 +5704,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>241</v>
+        <v>163</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5869,7 +5728,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
@@ -5877,23 +5736,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5901,7 +5760,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5909,7 +5768,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5917,7 +5776,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5925,7 +5784,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5933,7 +5792,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5941,7 +5800,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5949,7 +5808,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5963,23 +5822,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -6043,13 +5902,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="C6" s="3">
-        <v>7.3</v>
+        <v>7.0</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -6057,13 +5916,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>241</v>
+        <v>123</v>
       </c>
       <c r="C7" s="3">
-        <v>7.0</v>
+        <v>6.7</v>
       </c>
       <c r="D7" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6071,13 +5930,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>180</v>
+        <v>117</v>
       </c>
       <c r="C8" s="3">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6085,10 +5944,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="C9" s="3">
-        <v>5.3</v>
+        <v>5.0</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6099,13 +5958,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="C10" s="3">
-        <v>5.0</v>
+        <v>4.8</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -6113,13 +5972,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="D11" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6127,10 +5986,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C12" s="3">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -6141,13 +6000,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="C13" s="3">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6155,13 +6014,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C14" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6169,7 +6028,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -6183,13 +6042,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>141</v>
+        <v>255</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6209,21 +6068,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3">
@@ -6231,10 +6090,10 @@
         <v>53</v>
       </c>
       <c r="B3" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4">
@@ -6242,10 +6101,10 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6264,7 +6123,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -6272,15 +6131,15 @@
         <v>52</v>
       </c>
       <c r="B2" s="3">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6293,7 +6152,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -6301,10 +6160,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>276</v>
+        <v>172</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6312,14 +6171,22 @@
         <v>124</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6344,10 +6211,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6359,10 +6226,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6379,31 +6246,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3">
@@ -6411,28 +6278,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>79</v>
@@ -6443,31 +6310,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
@@ -6475,31 +6342,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>228</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6">
@@ -6507,28 +6374,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>275</v>
+        <v>171</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="F6" s="3">
         <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>115</v>
@@ -6539,31 +6406,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>294</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F7" s="3">
         <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
@@ -6571,31 +6438,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>327</v>
+        <v>415</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>241</v>
+        <v>416</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F8" s="3">
         <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>328</v>
+        <v>418</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
@@ -6603,31 +6470,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F9" s="3">
         <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>194</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10">
@@ -6635,31 +6502,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>429</v>
+        <v>166</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>178</v>
+        <v>312</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F10" s="3">
         <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>213</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11">
@@ -6667,31 +6534,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>342</v>
+        <v>181</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="F11" s="3">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>198</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -6699,31 +6566,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>178</v>
+        <v>430</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F12" s="3">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>43</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13">
@@ -6731,31 +6598,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>333</v>
+        <v>146</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>334</v>
+        <v>147</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F13" s="3">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>198</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -6763,31 +6630,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>445</v>
+        <v>410</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15">
@@ -6795,31 +6662,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>448</v>
+        <v>67</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>299</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>450</v>
+        <v>69</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -6827,31 +6694,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>241</v>
+        <v>439</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>452</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6859,31 +6726,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>228</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -6891,31 +6758,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>459</v>
+        <v>171</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F18" s="3">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19">
@@ -6923,31 +6790,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>457</v>
+        <v>328</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>145</v>
+        <v>358</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>146</v>
+        <v>450</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>43</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
@@ -6955,31 +6822,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21">
@@ -6987,31 +6854,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>67</v>
+        <v>457</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>63</v>
+        <v>458</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>69</v>
+        <v>460</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>70</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
